--- a/final_score_table/zscore_2023_wide.xlsx
+++ b/final_score_table/zscore_2023_wide.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ramra\OneDrive\Desktop\Individual Gentrification Project\gentrification-risk-index\final_score_table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86C42471-AF81-4645-A8D7-F2EC57CA0614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A253BA3A-77C1-4D3C-9927-DE129C181609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="2023 Z score " sheetId="1" r:id="rId1"/>
+    <sheet name="2023 Baseline" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
@@ -25,25 +25,25 @@
     <t>GEOID</t>
   </si>
   <si>
-    <t>education.csv_zscore</t>
+    <t>education</t>
   </si>
   <si>
-    <t>housing_tenure_burden.csv.csv_zscore</t>
+    <t>housing</t>
   </si>
   <si>
-    <t>income.csv_zscore</t>
+    <t>income</t>
   </si>
   <si>
-    <t>percent_white.csv_zscore</t>
+    <t>white</t>
   </si>
   <si>
-    <t>vacancy_rate.csv_zscore</t>
+    <t>vacancy</t>
   </si>
   <si>
-    <t>zhvi.csv_zscore</t>
+    <t>zhvi</t>
   </si>
   <si>
-    <t>zori.csv_zscore</t>
+    <t>zori</t>
   </si>
 </sst>
 </file>
@@ -396,10 +396,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:H309"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -425,7 +426,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>18097310103</v>
       </c>
@@ -445,7 +446,7 @@
         <v>1.2905590335893751</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>18097310104</v>
       </c>
@@ -471,7 +472,7 @@
         <v>0.97193231133569558</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>18097310105</v>
       </c>
@@ -497,7 +498,7 @@
         <v>0.97193231133569558</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>18097310106</v>
       </c>
@@ -523,7 +524,7 @@
         <v>0.87477912533881785</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>18097310108</v>
       </c>
@@ -549,7 +550,7 @@
         <v>1.3394234912806779</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>18097310110</v>
       </c>
@@ -575,7 +576,7 @@
         <v>0.68449806670121471</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>18097310111</v>
       </c>
@@ -601,7 +602,7 @@
         <v>0.68449806670121471</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>18097310112</v>
       </c>
@@ -624,7 +625,7 @@
         <v>2.666004563136898</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>18097310113</v>
       </c>
@@ -632,7 +633,7 @@
         <v>1.8024895493622051</v>
       </c>
       <c r="D10">
-        <v>4.2650717214228928</v>
+        <v>4</v>
       </c>
       <c r="E10">
         <v>0.68790474524588108</v>
@@ -647,7 +648,7 @@
         <v>1.8016276961293229</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>18097310201</v>
       </c>
@@ -673,7 +674,7 @@
         <v>0.97193231133569558</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>18097310203</v>
       </c>
@@ -699,7 +700,7 @@
         <v>0.97193231133569558</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>18097310204</v>
       </c>
@@ -725,7 +726,7 @@
         <v>0.95042017109566479</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>18097310305</v>
       </c>
@@ -751,7 +752,7 @@
         <v>0.68449806670121471</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>18097310306</v>
       </c>
@@ -777,7 +778,7 @@
         <v>0.68449806670121471</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>18097310308</v>
       </c>
@@ -803,7 +804,7 @@
         <v>-2.8562046718523688</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>18097310309</v>
       </c>
@@ -829,7 +830,7 @@
         <v>0.68449806670121471</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>18097310310</v>
       </c>
@@ -855,7 +856,7 @@
         <v>0.68449806670121471</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18097310311</v>
       </c>
@@ -881,7 +882,7 @@
         <v>-3.6100775423352509</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>18097310312</v>
       </c>
@@ -907,7 +908,7 @@
         <v>0.68449806670121471</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18097320105</v>
       </c>
@@ -933,7 +934,7 @@
         <v>0.1043242590372187</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>18097320106</v>
       </c>
@@ -959,7 +960,7 @@
         <v>0.1043242590372187</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>18097320107</v>
       </c>
@@ -985,7 +986,7 @@
         <v>0.1043242590372187</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>18097320108</v>
       </c>
@@ -1011,7 +1012,7 @@
         <v>0.1043242590372187</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>18097320109</v>
       </c>
@@ -1037,7 +1038,7 @@
         <v>0.1043242590372187</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>18097320202</v>
       </c>
@@ -1063,7 +1064,7 @@
         <v>0.34892577814529002</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>18097320203</v>
       </c>
@@ -1083,7 +1084,7 @@
         <v>0.3726353699465898</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>18097320204</v>
       </c>
@@ -1103,7 +1104,7 @@
         <v>-0.52672255278033853</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>18097320205</v>
       </c>
@@ -1123,7 +1124,7 @@
         <v>-1.2671511344873141</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>18097320206</v>
       </c>
@@ -1146,7 +1147,7 @@
         <v>1.225595982378217</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>18097320301</v>
       </c>
@@ -1172,7 +1173,7 @@
         <v>0.34892577814529002</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>18097320303</v>
       </c>
@@ -1192,7 +1193,7 @@
         <v>0.37819928666427399</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>18097320304</v>
       </c>
@@ -1212,7 +1213,7 @@
         <v>1.2905590335893751</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>18097320305</v>
       </c>
@@ -1238,7 +1239,7 @@
         <v>0.34892577814529002</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>18097320306</v>
       </c>
@@ -1264,7 +1265,7 @@
         <v>0.34892577814529002</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>18097320400</v>
       </c>
@@ -1290,7 +1291,7 @@
         <v>0.34892577814529002</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>18097320500</v>
       </c>
@@ -1316,7 +1317,7 @@
         <v>0.34892577814529002</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>18097320600</v>
       </c>
@@ -1342,7 +1343,7 @@
         <v>0.34892577814529002</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>18097320700</v>
       </c>
@@ -1368,7 +1369,7 @@
         <v>0.34874377904105752</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>18097320800</v>
       </c>
@@ -1379,7 +1380,7 @@
         <v>-1.365642538451709</v>
       </c>
       <c r="D40">
-        <v>4.1771114331089327</v>
+        <v>4</v>
       </c>
       <c r="E40">
         <v>1.5829458485572541</v>
@@ -1394,7 +1395,7 @@
         <v>0.1258218128714769</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>18097320901</v>
       </c>
@@ -1420,7 +1421,7 @@
         <v>0.1043242590372187</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>18097320902</v>
       </c>
@@ -1446,7 +1447,7 @@
         <v>0.1043242590372187</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>18097320903</v>
       </c>
@@ -1472,7 +1473,7 @@
         <v>0.10650275209972471</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>18097321001</v>
       </c>
@@ -1495,10 +1496,10 @@
         <v>0.51368803633609061</v>
       </c>
       <c r="H44">
-        <v>-4.1041014356197607</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>18097321002</v>
       </c>
@@ -1521,10 +1522,10 @@
         <v>0.50755068478767162</v>
       </c>
       <c r="H45">
-        <v>-4.2012080564124341</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>18097321100</v>
       </c>
@@ -1550,7 +1551,7 @@
         <v>-3.5128541876651962</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>18097321200</v>
       </c>
@@ -1576,7 +1577,7 @@
         <v>0.22503416837747689</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>18097321300</v>
       </c>
@@ -1602,7 +1603,7 @@
         <v>0.34892577814529002</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>18097321400</v>
       </c>
@@ -1628,7 +1629,7 @@
         <v>0.34892577814529002</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>18097321600</v>
       </c>
@@ -1654,7 +1655,7 @@
         <v>0.2363335613724849</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>18097321700</v>
       </c>
@@ -1680,7 +1681,7 @@
         <v>0.37553886669111702</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>18097321800</v>
       </c>
@@ -1706,7 +1707,7 @@
         <v>5.0721031668696272E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>18097321900</v>
       </c>
@@ -1732,7 +1733,7 @@
         <v>-0.40668521343758662</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>18097322000</v>
       </c>
@@ -1758,7 +1759,7 @@
         <v>-0.41052293503655962</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>18097322100</v>
       </c>
@@ -1784,7 +1785,7 @@
         <v>0.45999939031977549</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>18097322200</v>
       </c>
@@ -1810,7 +1811,7 @@
         <v>0.45999939031977549</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>18097322300</v>
       </c>
@@ -1836,7 +1837,7 @@
         <v>0.45999939031977549</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>18097322400</v>
       </c>
@@ -1862,7 +1863,7 @@
         <v>0.45999939031977549</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>18097322500</v>
       </c>
@@ -1888,7 +1889,7 @@
         <v>0.45999939031977549</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>18097322600</v>
       </c>
@@ -1908,7 +1909,7 @@
         <v>-0.74084712651643303</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>18097322601</v>
       </c>
@@ -1934,7 +1935,7 @@
         <v>0.36077388145090988</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>18097322602</v>
       </c>
@@ -1960,7 +1961,7 @@
         <v>0.45065669491128763</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>18097322700</v>
       </c>
@@ -1986,7 +1987,7 @@
         <v>-0.5471284696894041</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>18097330103</v>
       </c>
@@ -2012,7 +2013,7 @@
         <v>-0.20916479459436779</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>18097330105</v>
       </c>
@@ -2038,7 +2039,7 @@
         <v>-0.20916479459436779</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>18097330106</v>
       </c>
@@ -2064,7 +2065,7 @@
         <v>-0.20916479459436779</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>18097330107</v>
       </c>
@@ -2090,7 +2091,7 @@
         <v>-0.20916479459436779</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>18097330108</v>
       </c>
@@ -2116,7 +2117,7 @@
         <v>-0.20916479459436779</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>18097330109</v>
       </c>
@@ -2142,7 +2143,7 @@
         <v>-0.20916479459436779</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>18097330202</v>
       </c>
@@ -2162,7 +2163,7 @@
         <v>0.39939231296237909</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>18097330203</v>
       </c>
@@ -2173,7 +2174,7 @@
         <v>-2.6571310480762929</v>
       </c>
       <c r="D71">
-        <v>4.0305438595397671</v>
+        <v>4</v>
       </c>
       <c r="E71">
         <v>1.58330592686926</v>
@@ -2182,7 +2183,7 @@
         <v>1.088319588946959</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>18097330204</v>
       </c>
@@ -2208,7 +2209,7 @@
         <v>0.76586226334271801</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>18097330206</v>
       </c>
@@ -2228,7 +2229,7 @@
         <v>1.065399599132645</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>18097330208</v>
       </c>
@@ -2248,7 +2249,7 @@
         <v>0.86437490144121198</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>18097330209</v>
       </c>
@@ -2268,7 +2269,7 @@
         <v>0.68528763099169476</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>18097330210</v>
       </c>
@@ -2294,7 +2295,7 @@
         <v>0.76586226334271801</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>18097330211</v>
       </c>
@@ -2320,7 +2321,7 @@
         <v>0.76586226334271801</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>18097330212</v>
       </c>
@@ -2346,7 +2347,7 @@
         <v>0.76586226334271801</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>18097330213</v>
       </c>
@@ -2366,7 +2367,7 @@
         <v>0.26012015529182542</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>18097330401</v>
       </c>
@@ -2392,7 +2393,7 @@
         <v>4.934493325826602E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>18097330500</v>
       </c>
@@ -2418,7 +2419,7 @@
         <v>-0.53970766366636447</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>18097330600</v>
       </c>
@@ -2444,7 +2445,7 @@
         <v>-0.53970766366636447</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>18097330700</v>
       </c>
@@ -2464,7 +2465,7 @@
         <v>0.97405931099408682</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>18097330701</v>
       </c>
@@ -2490,7 +2491,7 @@
         <v>-0.53970766366636447</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>18097330702</v>
       </c>
@@ -2516,7 +2517,7 @@
         <v>0.56467449897947031</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>18097330803</v>
       </c>
@@ -2542,7 +2543,7 @@
         <v>0.76586226334271801</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>18097330804</v>
       </c>
@@ -2568,7 +2569,7 @@
         <v>0.75576857290219701</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>18097330805</v>
       </c>
@@ -2594,7 +2595,7 @@
         <v>-0.53970766366636447</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>18097330806</v>
       </c>
@@ -2620,7 +2621,7 @@
         <v>-0.53970766366636447</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>18097330900</v>
       </c>
@@ -2646,7 +2647,7 @@
         <v>-0.53970766366636447</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>18097331000</v>
       </c>
@@ -2672,7 +2673,7 @@
         <v>-0.54679400914616316</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>18097340101</v>
       </c>
@@ -2698,7 +2699,7 @@
         <v>0.73771862596238491</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>18097340102</v>
       </c>
@@ -2724,7 +2725,7 @@
         <v>-0.44503689959780368</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>18097340108</v>
       </c>
@@ -2750,7 +2751,7 @@
         <v>-0.66234733466801632</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>18097340109</v>
       </c>
@@ -2770,7 +2771,7 @@
         <v>-0.77598964599947062</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>18097340110</v>
       </c>
@@ -2790,7 +2791,7 @@
         <v>-3.6975387209147399E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>18097340111</v>
       </c>
@@ -2816,7 +2817,7 @@
         <v>-1.4326107038939001E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>18097340112</v>
       </c>
@@ -2842,7 +2843,7 @@
         <v>-0.17384263595335861</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>18097340113</v>
       </c>
@@ -2868,7 +2869,7 @@
         <v>1.732206545917031</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>18097340114</v>
       </c>
@@ -2894,7 +2895,7 @@
         <v>1.789025068419533</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>18097340115</v>
       </c>
@@ -2920,7 +2921,7 @@
         <v>-0.3463707335279288</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>18097340201</v>
       </c>
@@ -2946,7 +2947,7 @@
         <v>-0.66234733466801632</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>18097340202</v>
       </c>
@@ -2972,7 +2973,7 @@
         <v>-0.66234733466801632</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>18097340300</v>
       </c>
@@ -2992,7 +2993,7 @@
         <v>1.2905590335893751</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>18097340301</v>
       </c>
@@ -3018,7 +3019,7 @@
         <v>-0.66234733466801632</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>18097340302</v>
       </c>
@@ -3044,7 +3045,7 @@
         <v>-0.66234733466801632</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>18097340400</v>
       </c>
@@ -3070,7 +3071,7 @@
         <v>-1.0911090644828061</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>18097340500</v>
       </c>
@@ -3096,7 +3097,7 @@
         <v>-1.1065988425469031</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>18097340600</v>
       </c>
@@ -3122,7 +3123,7 @@
         <v>-1.1065988425469031</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>18097340700</v>
       </c>
@@ -3148,7 +3149,7 @@
         <v>-1.103731418519283</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>18097340800</v>
       </c>
@@ -3174,7 +3175,7 @@
         <v>-0.66234733466801632</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>18097340901</v>
       </c>
@@ -3200,7 +3201,7 @@
         <v>-0.3463707335279288</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>18097340902</v>
       </c>
@@ -3220,7 +3221,7 @@
         <v>0.83692046559506095</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>18097340903</v>
       </c>
@@ -3246,7 +3247,7 @@
         <v>-0.66234733466801632</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>18097340904</v>
       </c>
@@ -3272,7 +3273,7 @@
         <v>-0.66234733466801632</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>18097341000</v>
       </c>
@@ -3298,7 +3299,7 @@
         <v>-0.68279970478784324</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>18097341100</v>
       </c>
@@ -3324,7 +3325,7 @@
         <v>-1.1065988425469031</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>18097341200</v>
       </c>
@@ -3350,7 +3351,7 @@
         <v>-1.1065988425469031</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>18097341600</v>
       </c>
@@ -3376,7 +3377,7 @@
         <v>-1.1065988425469031</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>18097341700</v>
       </c>
@@ -3396,7 +3397,7 @@
         <v>-0.61017065554438976</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>18097341701</v>
       </c>
@@ -3422,7 +3423,7 @@
         <v>-1.1065988425469031</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>18097341702</v>
       </c>
@@ -3448,7 +3449,7 @@
         <v>-0.72374477419987537</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>18097341902</v>
       </c>
@@ -3474,7 +3475,7 @@
         <v>-0.2901245366147584</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>18097341903</v>
       </c>
@@ -3500,7 +3501,7 @@
         <v>-0.63108711295918551</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>18097341904</v>
       </c>
@@ -3526,7 +3527,7 @@
         <v>-0.66234733466801632</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>18097342000</v>
       </c>
@@ -3549,7 +3550,7 @@
         <v>0.38200013807202737</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>18097342101</v>
       </c>
@@ -3575,7 +3576,7 @@
         <v>-0.16042075161425759</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>18097342200</v>
       </c>
@@ -3601,7 +3602,7 @@
         <v>-4.2614130491711658E-2</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>18097342300</v>
       </c>
@@ -3627,7 +3628,7 @@
         <v>-4.2614130491711658E-2</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>18097342400</v>
       </c>
@@ -3653,7 +3654,7 @@
         <v>-3.4131325922294488E-2</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>18097342500</v>
       </c>
@@ -3679,7 +3680,7 @@
         <v>-4.2614130491711658E-2</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>18097342600</v>
       </c>
@@ -3705,7 +3706,7 @@
         <v>0.1183338531041961</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>18097350100</v>
       </c>
@@ -3731,7 +3732,7 @@
         <v>-0.45981175696823501</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>18097350300</v>
       </c>
@@ -3757,7 +3758,7 @@
         <v>-0.29766468519757688</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>18097350400</v>
       </c>
@@ -3783,7 +3784,7 @@
         <v>0.45999939031977549</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>18097350500</v>
       </c>
@@ -3809,7 +3810,7 @@
         <v>-0.97058205636513095</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>18097350600</v>
       </c>
@@ -3835,7 +3836,7 @@
         <v>-0.97058205636513095</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>18097350700</v>
       </c>
@@ -3861,7 +3862,7 @@
         <v>-0.97058205636513095</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>18097350800</v>
       </c>
@@ -3887,7 +3888,7 @@
         <v>-0.65608568754400587</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>18097350900</v>
       </c>
@@ -3913,7 +3914,7 @@
         <v>0.45999939031977549</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>18097351000</v>
       </c>
@@ -3936,7 +3937,7 @@
         <v>-0.22230165356737611</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>18097351200</v>
       </c>
@@ -3962,7 +3963,7 @@
         <v>-0.45981175696823501</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>18097351500</v>
       </c>
@@ -3988,7 +3989,7 @@
         <v>-0.2716450850033596</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>18097351600</v>
       </c>
@@ -4014,7 +4015,7 @@
         <v>6.7791427341195365E-2</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>18097351700</v>
       </c>
@@ -4040,7 +4041,7 @@
         <v>0.26873404471209128</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>18097351900</v>
       </c>
@@ -4066,7 +4067,7 @@
         <v>-0.97058205636513095</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>18097352100</v>
       </c>
@@ -4092,7 +4093,7 @@
         <v>-0.97058205636513095</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>18097352300</v>
       </c>
@@ -4118,7 +4119,7 @@
         <v>-0.97058205636513095</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>18097352400</v>
       </c>
@@ -4144,7 +4145,7 @@
         <v>-0.9652002582913346</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>18097352500</v>
       </c>
@@ -4170,7 +4171,7 @@
         <v>-0.80501978823325315</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>18097352600</v>
       </c>
@@ -4196,7 +4197,7 @@
         <v>-0.85134749151415234</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>18097352700</v>
       </c>
@@ -4222,7 +4223,7 @@
         <v>-0.81307310791225551</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>18097352800</v>
       </c>
@@ -4248,7 +4249,7 @@
         <v>-0.41528510429145982</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>18097353300</v>
       </c>
@@ -4274,7 +4275,7 @@
         <v>0.18751744104799969</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>18097353500</v>
       </c>
@@ -4300,7 +4301,7 @@
         <v>0.18751744104799969</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>18097353600</v>
       </c>
@@ -4326,7 +4327,7 @@
         <v>-4.5309027748890368E-2</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>18097354200</v>
       </c>
@@ -4346,7 +4347,7 @@
         <v>5.399966646117127E-2</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>18097354201</v>
       </c>
@@ -4372,7 +4373,7 @@
         <v>1.3366650609660251</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>18097354202</v>
       </c>
@@ -4398,7 +4399,7 @@
         <v>0.87152413116849203</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>18097354400</v>
       </c>
@@ -4424,7 +4425,7 @@
         <v>-8.1157819546852972E-2</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>18097354500</v>
       </c>
@@ -4450,7 +4451,7 @@
         <v>-0.79354021600757396</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>18097354700</v>
       </c>
@@ -4476,7 +4477,7 @@
         <v>-0.79354021600757396</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>18097354800</v>
       </c>
@@ -4502,7 +4503,7 @@
         <v>-0.79354021600757396</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>18097354900</v>
       </c>
@@ -4528,7 +4529,7 @@
         <v>-0.79354021600757396</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>18097355000</v>
       </c>
@@ -4554,7 +4555,7 @@
         <v>-0.79354021600757396</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>18097355100</v>
       </c>
@@ -4580,7 +4581,7 @@
         <v>-0.79354021600757396</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>18097355300</v>
       </c>
@@ -4606,7 +4607,7 @@
         <v>-0.81054524931239713</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>18097355400</v>
       </c>
@@ -4632,7 +4633,7 @@
         <v>-0.80172253528484794</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>18097355500</v>
       </c>
@@ -4658,7 +4659,7 @@
         <v>-0.52607915033144947</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>18097355600</v>
       </c>
@@ -4684,7 +4685,7 @@
         <v>-0.70822959302460486</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>18097355700</v>
       </c>
@@ -4710,7 +4711,7 @@
         <v>-0.50172010544857393</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>18097355900</v>
       </c>
@@ -4736,7 +4737,7 @@
         <v>-9.1708225654144243E-2</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>18097356200</v>
       </c>
@@ -4762,7 +4763,7 @@
         <v>0.61240529658822862</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>18097356400</v>
       </c>
@@ -4788,7 +4789,7 @@
         <v>-0.44480503164828877</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>18097356900</v>
       </c>
@@ -4811,7 +4812,7 @@
         <v>-0.80321477118194173</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>18097357000</v>
       </c>
@@ -4837,7 +4838,7 @@
         <v>-1.2075931916165059</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>18097357100</v>
       </c>
@@ -4863,7 +4864,7 @@
         <v>-7.2341362891557875E-2</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>18097357200</v>
       </c>
@@ -4889,7 +4890,7 @@
         <v>-7.2341362891557875E-2</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>18097357300</v>
       </c>
@@ -4915,7 +4916,7 @@
         <v>-7.2341362891557875E-2</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>18097357400</v>
       </c>
@@ -4941,7 +4942,7 @@
         <v>-7.2341362891557875E-2</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>18097357500</v>
       </c>
@@ -4967,7 +4968,7 @@
         <v>-7.2341362891557875E-2</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>18097357600</v>
       </c>
@@ -4987,7 +4988,7 @@
         <v>-2.792476196307776</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>18097357601</v>
       </c>
@@ -5013,7 +5014,7 @@
         <v>-7.2341362891557875E-2</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>18097357602</v>
       </c>
@@ -5039,7 +5040,7 @@
         <v>-7.2341362891557875E-2</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>18097357800</v>
       </c>
@@ -5065,7 +5066,7 @@
         <v>-2.8212110748014978</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>18097357900</v>
       </c>
@@ -5091,7 +5092,7 @@
         <v>-3.4986111840006879</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>18097358000</v>
       </c>
@@ -5114,7 +5115,7 @@
         <v>-0.80321477118194173</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>18097358100</v>
       </c>
@@ -5140,7 +5141,7 @@
         <v>0.61968755484914451</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>18097360101</v>
       </c>
@@ -5166,7 +5167,7 @@
         <v>-0.97058205636513095</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>18097360102</v>
       </c>
@@ -5192,7 +5193,7 @@
         <v>-0.97058205636513095</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>18097360201</v>
       </c>
@@ -5218,7 +5219,7 @@
         <v>-0.55839772529000331</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>18097360202</v>
       </c>
@@ -5244,7 +5245,7 @@
         <v>-0.53970766366636447</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>18097360301</v>
       </c>
@@ -5270,7 +5271,7 @@
         <v>-1.2635207218699851</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>18097360302</v>
       </c>
@@ -5296,7 +5297,7 @@
         <v>-1.2478618497489351</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>18097360401</v>
       </c>
@@ -5322,7 +5323,7 @@
         <v>1.07231352316838</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>18097360402</v>
       </c>
@@ -5348,7 +5349,7 @@
         <v>0.76586226334271801</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>18097360404</v>
       </c>
@@ -5368,7 +5369,7 @@
         <v>-1.7039469716462221</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>18097360405</v>
       </c>
@@ -5394,7 +5395,7 @@
         <v>1.0786113767706971</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>18097360406</v>
       </c>
@@ -5420,7 +5421,7 @@
         <v>0.76586226334271801</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>18097360407</v>
       </c>
@@ -5446,7 +5447,7 @@
         <v>0.77134108369847387</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>18097360501</v>
       </c>
@@ -5472,7 +5473,7 @@
         <v>1.0786113767706971</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>18097360502</v>
       </c>
@@ -5498,7 +5499,7 @@
         <v>1.0512961532932461</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>18097360601</v>
       </c>
@@ -5524,7 +5525,7 @@
         <v>-1.2635207218699851</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>18097360602</v>
       </c>
@@ -5550,7 +5551,7 @@
         <v>-1.263520721869984</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>18097360700</v>
       </c>
@@ -5576,7 +5577,7 @@
         <v>-1.2635207218699851</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>18097360800</v>
       </c>
@@ -5602,7 +5603,7 @@
         <v>-1.2635207218699851</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>18097360900</v>
       </c>
@@ -5628,7 +5629,7 @@
         <v>-1.122327299726414</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>18097361000</v>
       </c>
@@ -5654,7 +5655,7 @@
         <v>-1.2635207218699851</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>18097361100</v>
       </c>
@@ -5680,7 +5681,7 @@
         <v>-1.26275514099029</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>18097361200</v>
       </c>
@@ -5706,7 +5707,7 @@
         <v>-1.2472742638287539</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>18097361300</v>
       </c>
@@ -5732,7 +5733,7 @@
         <v>-1.2635207218699851</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>18097361400</v>
       </c>
@@ -5752,7 +5753,7 @@
         <v>-0.1993402600955366</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>18097361401</v>
       </c>
@@ -5778,7 +5779,7 @@
         <v>1.6220844038992011</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>18097361402</v>
       </c>
@@ -5804,7 +5805,7 @@
         <v>0.244600563999717</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>18097361600</v>
       </c>
@@ -5824,7 +5825,7 @@
         <v>1.12470885017922</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>18097361601</v>
       </c>
@@ -5850,7 +5851,7 @@
         <v>1.3890287343816621</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>18097361602</v>
       </c>
@@ -5876,7 +5877,7 @@
         <v>1.628030188256526</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>18097370201</v>
       </c>
@@ -5902,7 +5903,7 @@
         <v>0.61752252517919115</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>18097370202</v>
       </c>
@@ -5922,7 +5923,7 @@
         <v>0.10450105609783029</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>18097370203</v>
       </c>
@@ -5948,7 +5949,7 @@
         <v>-4.1583026089238632E-2</v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>18097370204</v>
       </c>
@@ -5974,7 +5975,7 @@
         <v>0.61968755484914451</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>18097370301</v>
       </c>
@@ -5994,7 +5995,7 @@
         <v>1.0801357907415849</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>18097370302</v>
       </c>
@@ -6014,7 +6015,7 @@
         <v>-0.143340167004814</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>18097370303</v>
       </c>
@@ -6040,7 +6041,7 @@
         <v>-7.7111638390943871E-2</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>18097370304</v>
       </c>
@@ -6066,7 +6067,7 @@
         <v>0.61968755484914451</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>18097370305</v>
       </c>
@@ -6092,7 +6093,7 @@
         <v>0.61968755484914451</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>18097370306</v>
       </c>
@@ -6118,7 +6119,7 @@
         <v>0.61968755484914606</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>18097380100</v>
       </c>
@@ -6138,7 +6139,7 @@
         <v>0.70724833833878153</v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>18097380101</v>
       </c>
@@ -6164,7 +6165,7 @@
         <v>1.182239424336855</v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>18097380102</v>
       </c>
@@ -6190,7 +6191,7 @@
         <v>1.182239424336855</v>
       </c>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>18097380103</v>
       </c>
@@ -6216,7 +6217,7 @@
         <v>1.1608913180984639</v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>18097380200</v>
       </c>
@@ -6242,7 +6243,7 @@
         <v>-1.1874412204820921</v>
       </c>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>18097380300</v>
       </c>
@@ -6262,7 +6263,7 @@
         <v>-2.4057223626749691</v>
       </c>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>18097380301</v>
       </c>
@@ -6288,7 +6289,7 @@
         <v>1.1293136303943141</v>
       </c>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>18097380302</v>
       </c>
@@ -6314,7 +6315,7 @@
         <v>-0.1522587060302808</v>
       </c>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>18097380402</v>
       </c>
@@ -6340,7 +6341,7 @@
         <v>1.1979180425978579</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>18097380403</v>
       </c>
@@ -6366,7 +6367,7 @@
         <v>-7.2341362891557875E-2</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>18097380404</v>
       </c>
@@ -6392,7 +6393,7 @@
         <v>0.97351960818348804</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>18097380501</v>
       </c>
@@ -6418,7 +6419,7 @@
         <v>-0.15364785821501961</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>18097380502</v>
       </c>
@@ -6444,7 +6445,7 @@
         <v>-0.15364785821501961</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>18097380600</v>
       </c>
@@ -6470,7 +6471,7 @@
         <v>0.2611223182340292</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>18097380700</v>
       </c>
@@ -6496,7 +6497,7 @@
         <v>0.53779005429804028</v>
       </c>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>18097380800</v>
       </c>
@@ -6522,7 +6523,7 @@
         <v>-0.15364785821501961</v>
       </c>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>18097380901</v>
       </c>
@@ -6548,7 +6549,7 @@
         <v>0.40204111474297988</v>
       </c>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>18097380902</v>
       </c>
@@ -6574,7 +6575,7 @@
         <v>1.1979180425978591</v>
       </c>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>18097381001</v>
       </c>
@@ -6594,7 +6595,7 @@
         <v>-1.1247344541003019</v>
       </c>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>18097381002</v>
       </c>
@@ -6620,7 +6621,7 @@
         <v>0.3779420515996722</v>
       </c>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>18097381003</v>
       </c>
@@ -6646,7 +6647,7 @@
         <v>-0.15364785821501961</v>
       </c>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>18097381004</v>
       </c>
@@ -6672,7 +6673,7 @@
         <v>-0.15364785821501961</v>
       </c>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>18097381101</v>
       </c>
@@ -6698,7 +6699,7 @@
         <v>0.64981701029242411</v>
       </c>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>18097381102</v>
       </c>
@@ -6724,7 +6725,7 @@
         <v>0.93638972969449241</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>18097381201</v>
       </c>
@@ -6744,7 +6745,7 @@
         <v>-0.26962199221350852</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>18097381203</v>
       </c>
@@ -6770,7 +6771,7 @@
         <v>-0.15364785821501961</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>18097381204</v>
       </c>
@@ -6796,7 +6797,7 @@
         <v>-0.15364785821501961</v>
       </c>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>18097381205</v>
       </c>
@@ -6822,7 +6823,7 @@
         <v>0.38075981377685991</v>
       </c>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>18097381206</v>
       </c>
@@ -6848,7 +6849,7 @@
         <v>-0.1440190943768257</v>
       </c>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>18097381207</v>
       </c>
@@ -6874,7 +6875,7 @@
         <v>1.182239424336855</v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>18097390101</v>
       </c>
@@ -6894,7 +6895,7 @@
         <v>1.1469502690525739</v>
       </c>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>18097390102</v>
       </c>
@@ -6920,7 +6921,7 @@
         <v>0.34975895622763681</v>
       </c>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>18097390103</v>
       </c>
@@ -6946,7 +6947,7 @@
         <v>0.9860912973223056</v>
       </c>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>18097390104</v>
       </c>
@@ -6972,7 +6973,7 @@
         <v>1.6148726358386649</v>
       </c>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>18097390200</v>
       </c>
@@ -6998,7 +6999,7 @@
         <v>1.628030188256526</v>
       </c>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>18097390300</v>
       </c>
@@ -7024,7 +7025,7 @@
         <v>1.628030188256526</v>
       </c>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>18097390402</v>
       </c>
@@ -7044,7 +7045,7 @@
         <v>0.79683477459482366</v>
       </c>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>18097390403</v>
       </c>
@@ -7064,7 +7065,7 @@
         <v>1.260932543149716</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>18097390404</v>
       </c>
@@ -7084,7 +7085,7 @@
         <v>1.2905590335893751</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>18097390405</v>
       </c>
@@ -7110,7 +7111,7 @@
         <v>1.1979180425978591</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>18097390406</v>
       </c>
@@ -7136,7 +7137,7 @@
         <v>1.628030188256526</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>18097390407</v>
       </c>
@@ -7156,7 +7157,7 @@
         <v>1.140094647665463</v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>18097390408</v>
       </c>
@@ -7182,7 +7183,7 @@
         <v>1.2010961753856511</v>
       </c>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>18097390409</v>
       </c>
@@ -7208,7 +7209,7 @@
         <v>1.1979180425978591</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>18097390410</v>
       </c>
@@ -7234,7 +7235,7 @@
         <v>1.1979180425978591</v>
       </c>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>18097390411</v>
       </c>
@@ -7260,7 +7261,7 @@
         <v>1.1979180425978591</v>
       </c>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>18097390500</v>
       </c>
@@ -7286,7 +7287,7 @@
         <v>-0.45981175696823501</v>
       </c>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>18097390600</v>
       </c>
@@ -7306,7 +7307,7 @@
         <v>0.14757485779739951</v>
       </c>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>18097390601</v>
       </c>
@@ -7332,7 +7333,7 @@
         <v>-0.53970766366636447</v>
       </c>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>18097390602</v>
       </c>
@@ -7358,7 +7359,7 @@
         <v>-0.53829427032953536</v>
       </c>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>18097390700</v>
       </c>
@@ -7384,7 +7385,7 @@
         <v>-1.1065988425469031</v>
       </c>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>18097390800</v>
       </c>
@@ -7404,7 +7405,7 @@
         <v>-1.841067292221783</v>
       </c>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>18097390801</v>
       </c>
@@ -7415,7 +7416,7 @@
         <v>-4.2614130491711658E-2</v>
       </c>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>18097390802</v>
       </c>
@@ -7441,7 +7442,7 @@
         <v>0.20202155529474791</v>
       </c>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>18097390900</v>
       </c>
@@ -7467,7 +7468,7 @@
         <v>0.18751744104799969</v>
       </c>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>18097391000</v>
       </c>
@@ -7487,7 +7488,7 @@
         <v>1.2845067930930829</v>
       </c>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>18097391001</v>
       </c>
@@ -7513,7 +7514,7 @@
         <v>-1.1330246167171101</v>
       </c>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>18097391002</v>
       </c>
@@ -7539,7 +7540,7 @@
         <v>1.2156007264882911</v>
       </c>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>18011810605</v>
       </c>
@@ -7550,7 +7551,7 @@
         <v>0.97193231133569558</v>
       </c>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>18057110805</v>
       </c>
@@ -7561,7 +7562,7 @@
         <v>-0.20916479459436779</v>
       </c>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>18057110807</v>
       </c>
@@ -7572,7 +7573,7 @@
         <v>-0.20916479459436779</v>
       </c>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>18057110810</v>
       </c>
@@ -7583,7 +7584,7 @@
         <v>-0.20916479459436779</v>
       </c>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>18057110813</v>
       </c>
@@ -7594,7 +7595,7 @@
         <v>-0.20916479459436779</v>
       </c>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>18057110822</v>
       </c>
@@ -7605,7 +7606,7 @@
         <v>-0.20916479459436779</v>
       </c>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>18057111006</v>
       </c>
@@ -7613,7 +7614,7 @@
         <v>1.225595982378217</v>
       </c>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>18057111101</v>
       </c>
@@ -7621,7 +7622,7 @@
         <v>1.225595982378217</v>
       </c>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>18057111103</v>
       </c>
@@ -7632,7 +7633,7 @@
         <v>0.56850682712487299</v>
       </c>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>18057111104</v>
       </c>
@@ -7640,7 +7641,7 @@
         <v>1.225595982378217</v>
       </c>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>18059410801</v>
       </c>
@@ -7651,7 +7652,7 @@
         <v>1.0810426707168239</v>
       </c>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>18059410802</v>
       </c>
@@ -7662,7 +7663,7 @@
         <v>1.628030188256526</v>
       </c>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>18059410901</v>
       </c>
@@ -7673,7 +7674,7 @@
         <v>1.0567458220576851</v>
       </c>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>18059410902</v>
       </c>
@@ -7684,7 +7685,7 @@
         <v>1.0786113767706971</v>
       </c>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>18063210106</v>
       </c>
@@ -7695,7 +7696,7 @@
         <v>1.8016276961293241</v>
       </c>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>18063210107</v>
       </c>
@@ -7703,7 +7704,7 @@
         <v>2.666004563136898</v>
       </c>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>18063210108</v>
       </c>
@@ -7714,7 +7715,7 @@
         <v>1.8016276961293229</v>
       </c>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>18063210109</v>
       </c>
@@ -7725,7 +7726,7 @@
         <v>1.8016276961293229</v>
       </c>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>18063210607</v>
       </c>
@@ -7733,7 +7734,7 @@
         <v>0.38200013807202737</v>
       </c>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>18063210608</v>
       </c>
@@ -7741,7 +7742,7 @@
         <v>0.38200013807202737</v>
       </c>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>18063210611</v>
       </c>
@@ -7752,7 +7753,7 @@
         <v>1.8016276961293229</v>
       </c>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>18063210614</v>
       </c>
@@ -7760,7 +7761,7 @@
         <v>0.38200013807202737</v>
       </c>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>18063210616</v>
       </c>
@@ -7771,7 +7772,7 @@
         <v>1.8016276961293229</v>
       </c>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>18063210617</v>
       </c>
